--- a/sample-files/AgencyC_Submissions.xlsx
+++ b/sample-files/AgencyC_Submissions.xlsx
@@ -423,7 +423,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -559,7 +558,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dimples</t>
+          <t>DIMPLES</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -643,12 +642,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Grey streak</t>
+          <t>Religious headwear</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Bangles</t>
+          <t>Makeup, Necklace</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
